--- a/Web/TestCases/Logout.xlsx
+++ b/Web/TestCases/Logout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C23B43-FECC-4D95-B165-0BB1808EB563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7EB281-1CB3-40AC-8152-CC096ACDEB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="26850" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,6 @@
     <t>Pasos</t>
   </si>
   <si>
-    <t>Logout</t>
-  </si>
-  <si>
-    <t>I logout from Home</t>
-  </si>
-  <si>
     <t>Expected Result</t>
   </si>
   <si>
@@ -60,6 +54,12 @@
   </si>
   <si>
     <t>1. the user logs out correctly.</t>
+  </si>
+  <si>
+    <t>LOG001</t>
+  </si>
+  <si>
+    <t>Logout page home</t>
   </si>
 </sst>
 </file>
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -125,11 +125,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -468,16 +533,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -485,31 +550,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="H2" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
